--- a/examples/synthea/specs/member_quality_summary.xlsx
+++ b/examples/synthea/specs/member_quality_summary.xlsx
@@ -1395,7 +1395,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S6"/>
+  <dimension ref="A1:S7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1703,6 +1703,46 @@
       <c r="P6" s="2" t="inlineStr"/>
       <c r="Q6" s="2" t="inlineStr"/>
       <c r="R6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>latest_a1c</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr"/>
+      <c r="C7" s="2" t="inlineStr"/>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>DECIMAL</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr"/>
+      <c r="F7" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" s="2" t="n"/>
+      <c r="I7" s="2" t="n"/>
+      <c r="J7" s="2" t="n"/>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>Most recent Hemoglobin A1c result for the patient.</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr"/>
+      <c r="O7" s="2" t="inlineStr"/>
+      <c r="P7" s="2" t="inlineStr"/>
+      <c r="Q7" s="2" t="inlineStr"/>
+      <c r="R7" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="6">
@@ -1735,7 +1775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2051,6 +2091,59 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>latest_a1c</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr"/>
+      <c r="D13" s="7" t="inlineStr"/>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>survivorship</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>most_recent</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr"/>
+      <c r="H13" s="7" t="inlineStr"/>
+      <c r="I13" s="8" t="inlineStr">
+        <is>
+          <t>Strategy: take the most recent qualifying A1c observation.
+Default: null when the patient has no A1c on file.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" outlineLevel="1">
+      <c r="A14" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B14" s="7" t="inlineStr"/>
+      <c r="C14" s="7" t="inlineStr"/>
+      <c r="D14" s="7" t="inlineStr"/>
+      <c r="E14" s="7" t="inlineStr"/>
+      <c r="F14" s="7" t="inlineStr"/>
+      <c r="G14" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>observations.VALUE</t>
+        </is>
+      </c>
+      <c r="I14" s="8" t="inlineStr">
+        <is>
+          <t>Latest A1c observation by observation date.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2062,7 +2155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:Q8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2103,15 +2196,50 @@
       </c>
       <c r="H1" s="5" t="inlineStr">
         <is>
+          <t>Row Filter</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
+          <t>Order By</t>
+        </is>
+      </c>
+      <c r="J1" s="5" t="inlineStr">
+        <is>
+          <t>Select Columns</t>
+        </is>
+      </c>
+      <c r="K1" s="5" t="inlineStr">
+        <is>
+          <t>Join Via</t>
+        </is>
+      </c>
+      <c r="L1" s="5" t="inlineStr">
+        <is>
           <t>Reason</t>
         </is>
       </c>
-      <c r="I1" s="5" t="inlineStr">
-        <is>
-          <t>Strategy</t>
-        </is>
-      </c>
-      <c r="J1" s="5" t="inlineStr">
+      <c r="M1" s="5" t="inlineStr">
+        <is>
+          <t>Derivation Strategy</t>
+        </is>
+      </c>
+      <c r="N1" s="5" t="inlineStr">
+        <is>
+          <t>Survivorship Strategy</t>
+        </is>
+      </c>
+      <c r="O1" s="5" t="inlineStr">
+        <is>
+          <t>Default Value</t>
+        </is>
+      </c>
+      <c r="P1" s="5" t="inlineStr">
+        <is>
+          <t>Default Condition</t>
+        </is>
+      </c>
+      <c r="Q1" s="5" t="inlineStr">
         <is>
           <t>Survivorship Explanation</t>
         </is>
@@ -2139,13 +2267,20 @@
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>One summary row per patient, keyed by the patient id.</t>
-        </is>
-      </c>
+      <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>One summary row per patient, keyed by the patient id.</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr"/>
+      <c r="N2" s="2" t="inlineStr"/>
+      <c r="O2" s="2" t="inlineStr"/>
+      <c r="P2" s="2" t="inlineStr"/>
+      <c r="Q2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -2169,13 +2304,20 @@
       </c>
       <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Latest BMI observation by observation date.</t>
-        </is>
-      </c>
+      <c r="H3" s="2" t="inlineStr"/>
       <c r="I3" s="2" t="inlineStr"/>
       <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Latest BMI observation by observation date.</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr"/>
+      <c r="N3" s="2" t="inlineStr"/>
+      <c r="O3" s="2" t="inlineStr"/>
+      <c r="P3" s="2" t="inlineStr"/>
+      <c r="Q3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -2203,13 +2345,20 @@
       </c>
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>SNOMED 44054006 = Diabetes mellitus type 2.</t>
-        </is>
-      </c>
+      <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>SNOMED 44054006 = Diabetes mellitus type 2.</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr"/>
+      <c r="N4" s="2" t="inlineStr"/>
+      <c r="O4" s="2" t="inlineStr"/>
+      <c r="P4" s="2" t="inlineStr"/>
+      <c r="Q4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -2237,17 +2386,24 @@
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>Prefer the provider whose specialty is general practice.</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>highest_priority</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr"/>
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>Strategy: choose the patient's general-practice provider when one exists.
 Fallback: if no GP is assigned, use the provider from the patient's most recent encounter.
@@ -2281,13 +2437,20 @@
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Fall back to the most recent encounter's provider.</t>
-        </is>
-      </c>
+      <c r="H6" s="2" t="inlineStr"/>
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>Fall back to the most recent encounter's provider.</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr"/>
+      <c r="O6" s="2" t="inlineStr"/>
+      <c r="P6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2315,13 +2478,82 @@
       </c>
       <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>Distinct encounters per patient.</t>
-        </is>
-      </c>
+      <c r="H7" s="2" t="inlineStr"/>
       <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>Distinct encounters per patient.</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr"/>
+      <c r="O7" s="2" t="inlineStr"/>
+      <c r="P7" s="2" t="inlineStr"/>
+      <c r="Q7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>latest_a1c</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>observations</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>VALUE</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>DESCRIPTION = 'Hemoglobin A1c/Hemoglobin.total in Blood'</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>["DATE"]</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>["VALUE", "UNITS"]</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>Latest A1c observation by observation date.</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>most_recent</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr"/>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>when no A1c observation exists</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>Strategy: take the most recent qualifying A1c observation.
+Default: null when the patient has no A1c on file.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
